--- a/Business analytics and intelligence/Isle Of Scilly /islesofscilly.xlsx
+++ b/Business analytics and intelligence/Isle Of Scilly /islesofscilly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/prw332/Documents/github/Notebooks_Python/Business analytics and intelligence/Isle Of Scilly /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{B2B53F40-204F-CD4D-AA46-8BC0CF6D4E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{C4B9834B-4440-7A4E-BF19-CD295A69EE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15480" activeTab="1"/>
   </bookViews>
@@ -28,15 +28,15 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$J$311</definedName>
     <definedName name="_xlchart.v1.0" hidden="1">data!$C$1</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">data!$C$2:$C$311</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Classes!$K$1</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Classes!$E$1</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">data!$D$1</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">data!$D$2:$D$311</definedName>
     <definedName name="_xlchart.v1.4" hidden="1">data!$C$1</definedName>
     <definedName name="_xlchart.v1.5" hidden="1">data!$C$2:$C$311</definedName>
     <definedName name="_xlchart.v1.6" hidden="1">data!$D$1</definedName>
     <definedName name="_xlchart.v1.7" hidden="1">data!$D$2:$D$311</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Classes!$D$2:$D$53</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Classes!$G$1:$G$34</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Classes!#REF!</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Classes!$A$1:$A$34</definedName>
     <definedName name="Prices">data!$C$2:$C$311</definedName>
     <definedName name="types">data!$H$2:$H$311</definedName>
     <definedName name="Years">data!$E$2:$E$311</definedName>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="656" uniqueCount="36">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="666" uniqueCount="37">
   <si>
     <t>Name</t>
   </si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>Class width</t>
+  </si>
+  <si>
+    <t>Years</t>
   </si>
   <si>
     <t>Row Labels</t>
@@ -741,7 +744,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -758,6 +761,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3054,7 +3058,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Classes!$K$1</c:f>
+              <c:f>Classes!$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3094,7 +3098,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Classes!$G$1:$G$34</c:f>
+              <c:f>Classes!$A$1:$A$34</c:f>
               <c:strCache>
                 <c:ptCount val="34"/>
                 <c:pt idx="0">
@@ -3204,10 +3208,115 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Classes!$D$2:$D$53</c:f>
+              <c:f>Classes!$E$1:$E$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="35"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3462,7 +3571,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Classes!$K$1</c:f>
+              <c:f>Classes!$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3485,7 +3594,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Classes!$G$1:$G$34</c:f>
+              <c:f>Classes!$A$1:$A$34</c:f>
               <c:strCache>
                 <c:ptCount val="34"/>
                 <c:pt idx="0">
@@ -3595,7 +3704,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Classes!$K$2:$K$35</c:f>
+              <c:f>Classes!$E$2:$E$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="34"/>
@@ -3993,7 +4102,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Classes!$M$1</c:f>
+              <c:f>Classes!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4014,7 +4123,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Classes!$G$1:$G$34</c:f>
+              <c:f>Classes!$A$1:$A$34</c:f>
               <c:strCache>
                 <c:ptCount val="34"/>
                 <c:pt idx="0">
@@ -4124,7 +4233,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Classes!$M$2:$M$34</c:f>
+              <c:f>Classes!$G$2:$G$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
@@ -4307,20 +4416,6 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15%"/>
-                  <a:lumOff val="85%"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -4532,7 +4627,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Classes!$M$1</c:f>
+              <c:f>Classes!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4555,7 +4650,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Classes!$G$1:$G$34</c:f>
+              <c:f>Classes!$A$1:$A$34</c:f>
               <c:strCache>
                 <c:ptCount val="34"/>
                 <c:pt idx="0">
@@ -4665,7 +4760,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Classes!$M$2:$M$34</c:f>
+              <c:f>Classes!$G$2:$G$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
@@ -14232,7 +14327,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A1:G20" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0">
@@ -24727,7 +24822,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.1640625" customWidth="1"/>
@@ -24820,6 +24915,92 @@
         <v>1555496</v>
       </c>
     </row>
+    <row r="13" spans="1:2" ht="26" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="12">
+        <f>_xlfn.QUARTILE.INC(Years, 0)</f>
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="12">
+        <f>_xlfn.QUARTILE.INC(Years, 1)</f>
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="12">
+        <f>_xlfn.MODE.SNGL(Years)</f>
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="12">
+        <f>_xlfn.QUARTILE.INC(Years, 2)</f>
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="12">
+        <f>AVERAGE(Years)</f>
+        <v>2008.8387096774193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="12">
+        <f>STDEV(Years)</f>
+        <v>5.1470088978990294</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="12">
+        <f>B21-B15</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="12">
+        <f>_xlfn.QUARTILE.INC(Years, 3)</f>
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="12">
+        <f>_xlfn.QUARTILE.INC(Prices,4 )</f>
+        <v>1555496</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24827,1080 +25008,1005 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:M53"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.1640625" customWidth="1"/>
-    <col min="8" max="8" width="18.5" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:13" ht="51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="G1" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="str">
+        <f>_xlfn.CONCAT(B2, " - ", C2)</f>
+        <v>0 - 49999</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <f>B2+49999</f>
+        <v>49999</v>
+      </c>
+      <c r="D2" s="3">
+        <f>C2-B2</f>
+        <v>49999</v>
+      </c>
+      <c r="E2" cm="1">
+        <f t="array" ref="E2:E35">FREQUENCY(Prices,C2:C34)</f>
+        <v>5</v>
+      </c>
+      <c r="F2" s="8">
+        <f>E2/D2</f>
+        <v>1.0000200004000079E-4</v>
+      </c>
+      <c r="G2">
+        <f>E2</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="str">
+        <f t="shared" ref="A3:A34" si="0">_xlfn.CONCAT(B3, " - ", C3)</f>
+        <v>50000 - 99999</v>
+      </c>
+      <c r="B3" s="3">
+        <f>C2+1</f>
+        <v>50000</v>
+      </c>
+      <c r="C3" s="3">
+        <f t="shared" ref="C3:C34" si="1">B3+49999</f>
+        <v>99999</v>
+      </c>
+      <c r="D3" s="3">
+        <f t="shared" ref="D3:D34" si="2">C3-B3</f>
+        <v>49999</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3" s="8">
+        <f t="shared" ref="F3:F35" si="3">E3/D3</f>
+        <v>2.0000400008000159E-4</v>
+      </c>
+      <c r="G3">
+        <f>G2+E3</f>
         <v>15</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G2" t="str">
-        <f>_xlfn.CONCAT(H2, " - ", I2)</f>
-        <v>0 - 49999</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3">
-        <f>H2+49999</f>
-        <v>49999</v>
-      </c>
-      <c r="J2" s="3">
-        <f>I2-H2</f>
-        <v>49999</v>
-      </c>
-      <c r="K2" cm="1">
-        <f t="array" ref="K2:K35">FREQUENCY(Prices,I2:I34)</f>
-        <v>5</v>
-      </c>
-      <c r="L2" s="8">
-        <f>K2/J2</f>
-        <v>1.0000200004000079E-4</v>
-      </c>
-      <c r="M2">
-        <f>K2</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G3" t="str">
-        <f t="shared" ref="G3:G34" si="0">_xlfn.CONCAT(H3, " - ", I3)</f>
-        <v>50000 - 99999</v>
-      </c>
-      <c r="H3" s="3">
-        <f>I2+1</f>
-        <v>50000</v>
-      </c>
-      <c r="I3" s="3">
-        <f t="shared" ref="I3:I34" si="1">H3+49999</f>
-        <v>99999</v>
-      </c>
-      <c r="J3" s="3">
-        <f t="shared" ref="J3:J34" si="2">I3-H3</f>
-        <v>49999</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3" s="8">
-        <f t="shared" ref="L3:L35" si="3">K3/J3</f>
-        <v>2.0000400008000159E-4</v>
-      </c>
-      <c r="M3">
-        <f>M2+K3</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G4" t="str">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>100000 - 149999</v>
       </c>
-      <c r="H4" s="3">
-        <f t="shared" ref="H4:H34" si="4">I3+1</f>
+      <c r="B4" s="3">
+        <f t="shared" ref="B4:B34" si="4">C3+1</f>
         <v>100000</v>
       </c>
-      <c r="I4" s="3">
+      <c r="C4" s="3">
         <f t="shared" si="1"/>
         <v>149999</v>
       </c>
-      <c r="J4" s="3">
+      <c r="D4" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K4">
+      <c r="E4">
         <v>12</v>
       </c>
-      <c r="L4" s="8">
+      <c r="F4" s="8">
         <f t="shared" si="3"/>
         <v>2.4000480009600192E-4</v>
       </c>
-      <c r="M4">
-        <f t="shared" ref="M4:M35" si="5">M3+K4</f>
+      <c r="G4">
+        <f t="shared" ref="G4:G35" si="5">G3+E4</f>
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G5" t="str">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>150000 - 199999</v>
       </c>
-      <c r="H5" s="3">
+      <c r="B5" s="3">
         <f t="shared" si="4"/>
         <v>150000</v>
       </c>
-      <c r="I5" s="3">
+      <c r="C5" s="3">
         <f t="shared" si="1"/>
         <v>199999</v>
       </c>
-      <c r="J5" s="3">
+      <c r="D5" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K5">
+      <c r="E5">
         <v>32</v>
       </c>
-      <c r="L5" s="8">
+      <c r="F5" s="8">
         <f t="shared" si="3"/>
         <v>6.4001280025600515E-4</v>
       </c>
-      <c r="M5">
+      <c r="G5">
         <f t="shared" si="5"/>
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G6" t="str">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>200000 - 249999</v>
       </c>
-      <c r="H6" s="3">
+      <c r="B6" s="3">
         <f t="shared" si="4"/>
         <v>200000</v>
       </c>
-      <c r="I6" s="3">
+      <c r="C6" s="3">
         <f t="shared" si="1"/>
         <v>249999</v>
       </c>
-      <c r="J6" s="3">
+      <c r="D6" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K6">
+      <c r="E6">
         <v>60</v>
       </c>
-      <c r="L6" s="8">
+      <c r="F6" s="8">
         <f t="shared" si="3"/>
         <v>1.2000240004800095E-3</v>
       </c>
-      <c r="M6">
+      <c r="G6">
         <f t="shared" si="5"/>
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G7" t="str">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>250000 - 299999</v>
       </c>
-      <c r="H7" s="3">
+      <c r="B7" s="3">
         <f t="shared" si="4"/>
         <v>250000</v>
       </c>
-      <c r="I7" s="3">
+      <c r="C7" s="3">
         <f t="shared" si="1"/>
         <v>299999</v>
       </c>
-      <c r="J7" s="3">
+      <c r="D7" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K7">
+      <c r="E7">
         <v>38</v>
       </c>
-      <c r="L7" s="8">
+      <c r="F7" s="8">
         <f t="shared" si="3"/>
         <v>7.6001520030400608E-4</v>
       </c>
-      <c r="M7">
+      <c r="G7">
         <f t="shared" si="5"/>
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G8" t="str">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>300000 - 349999</v>
       </c>
-      <c r="H8" s="3">
+      <c r="B8" s="3">
         <f t="shared" si="4"/>
         <v>300000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="C8" s="3">
         <f t="shared" si="1"/>
         <v>349999</v>
       </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K8">
+      <c r="E8">
         <v>38</v>
       </c>
-      <c r="L8" s="8">
+      <c r="F8" s="8">
         <f t="shared" si="3"/>
         <v>7.6001520030400608E-4</v>
       </c>
-      <c r="M8">
+      <c r="G8">
         <f t="shared" si="5"/>
         <v>195</v>
       </c>
     </row>
-    <row r="9" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G9" t="str">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>350000 - 399999</v>
       </c>
-      <c r="H9" s="3">
+      <c r="B9" s="3">
         <f t="shared" si="4"/>
         <v>350000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="C9" s="3">
         <f t="shared" si="1"/>
         <v>399999</v>
       </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K9">
+      <c r="E9">
         <v>33</v>
       </c>
-      <c r="L9" s="8">
+      <c r="F9" s="8">
         <f t="shared" si="3"/>
         <v>6.6001320026400523E-4</v>
       </c>
-      <c r="M9">
+      <c r="G9">
         <f t="shared" si="5"/>
         <v>228</v>
       </c>
     </row>
-    <row r="10" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G10" t="str">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>400000 - 449999</v>
       </c>
-      <c r="H10" s="3">
+      <c r="B10" s="3">
         <f t="shared" si="4"/>
         <v>400000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="C10" s="3">
         <f t="shared" si="1"/>
         <v>449999</v>
       </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K10">
+      <c r="E10">
         <v>32</v>
       </c>
-      <c r="L10" s="8">
+      <c r="F10" s="8">
         <f t="shared" si="3"/>
         <v>6.4001280025600515E-4</v>
       </c>
-      <c r="M10">
+      <c r="G10">
         <f t="shared" si="5"/>
         <v>260</v>
       </c>
     </row>
-    <row r="11" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G11" t="str">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>450000 - 499999</v>
       </c>
-      <c r="H11" s="3">
+      <c r="B11" s="3">
         <f t="shared" si="4"/>
         <v>450000</v>
       </c>
-      <c r="I11" s="3">
+      <c r="C11" s="3">
         <f t="shared" si="1"/>
         <v>499999</v>
       </c>
-      <c r="J11" s="3">
+      <c r="D11" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K11">
+      <c r="E11">
         <v>22</v>
       </c>
-      <c r="L11" s="8">
+      <c r="F11" s="8">
         <f t="shared" si="3"/>
         <v>4.4000880017600351E-4</v>
       </c>
-      <c r="M11">
+      <c r="G11">
         <f t="shared" si="5"/>
         <v>282</v>
       </c>
     </row>
-    <row r="12" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G12" t="str">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>500000 - 549999</v>
       </c>
-      <c r="H12" s="3">
+      <c r="B12" s="3">
         <f t="shared" si="4"/>
         <v>500000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="C12" s="3">
         <f t="shared" si="1"/>
         <v>549999</v>
       </c>
-      <c r="J12" s="3">
+      <c r="D12" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K12">
+      <c r="E12">
         <v>7</v>
       </c>
-      <c r="L12" s="8">
+      <c r="F12" s="8">
         <f t="shared" si="3"/>
         <v>1.4000280005600112E-4</v>
       </c>
-      <c r="M12">
+      <c r="G12">
         <f t="shared" si="5"/>
         <v>289</v>
       </c>
     </row>
-    <row r="13" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G13" t="str">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="str">
         <f t="shared" si="0"/>
         <v>550000 - 599999</v>
       </c>
-      <c r="H13" s="3">
+      <c r="B13" s="3">
         <f t="shared" si="4"/>
         <v>550000</v>
       </c>
-      <c r="I13" s="3">
+      <c r="C13" s="3">
         <f t="shared" si="1"/>
         <v>599999</v>
       </c>
-      <c r="J13" s="3">
+      <c r="D13" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K13">
+      <c r="E13">
         <v>4</v>
       </c>
-      <c r="L13" s="8">
+      <c r="F13" s="8">
         <f t="shared" si="3"/>
         <v>8.0001600032000644E-5</v>
       </c>
-      <c r="M13">
+      <c r="G13">
         <f t="shared" si="5"/>
         <v>293</v>
       </c>
     </row>
-    <row r="14" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G14" t="str">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="str">
         <f t="shared" si="0"/>
         <v>600000 - 649999</v>
       </c>
-      <c r="H14" s="3">
+      <c r="B14" s="3">
         <f t="shared" si="4"/>
         <v>600000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="C14" s="3">
         <f t="shared" si="1"/>
         <v>649999</v>
       </c>
-      <c r="J14" s="3">
+      <c r="D14" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K14">
+      <c r="E14">
         <v>3</v>
       </c>
-      <c r="L14" s="8">
+      <c r="F14" s="8">
         <f t="shared" si="3"/>
         <v>6.0001200024000479E-5</v>
       </c>
-      <c r="M14">
+      <c r="G14">
         <f t="shared" si="5"/>
         <v>296</v>
       </c>
     </row>
-    <row r="15" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G15" t="str">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>650000 - 699999</v>
       </c>
-      <c r="H15" s="3">
+      <c r="B15" s="3">
         <f t="shared" si="4"/>
         <v>650000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="C15" s="3">
         <f t="shared" si="1"/>
         <v>699999</v>
       </c>
-      <c r="J15" s="3">
+      <c r="D15" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K15">
+      <c r="E15">
         <v>3</v>
       </c>
-      <c r="L15" s="8">
+      <c r="F15" s="8">
         <f t="shared" si="3"/>
         <v>6.0001200024000479E-5</v>
       </c>
-      <c r="M15">
+      <c r="G15">
         <f t="shared" si="5"/>
         <v>299</v>
       </c>
     </row>
-    <row r="16" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G16" t="str">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="str">
         <f t="shared" si="0"/>
         <v>700000 - 749999</v>
       </c>
-      <c r="H16" s="3">
+      <c r="B16" s="3">
         <f t="shared" si="4"/>
         <v>700000</v>
       </c>
-      <c r="I16" s="3">
+      <c r="C16" s="3">
         <f t="shared" si="1"/>
         <v>749999</v>
       </c>
-      <c r="J16" s="3">
+      <c r="D16" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K16">
+      <c r="E16">
         <v>5</v>
       </c>
-      <c r="L16" s="8">
+      <c r="F16" s="8">
         <f t="shared" si="3"/>
         <v>1.0000200004000079E-4</v>
       </c>
-      <c r="M16">
+      <c r="G16">
         <f t="shared" si="5"/>
         <v>304</v>
       </c>
     </row>
-    <row r="17" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G17" t="str">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>750000 - 799999</v>
       </c>
-      <c r="H17" s="3">
+      <c r="B17" s="3">
         <f t="shared" si="4"/>
         <v>750000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="C17" s="3">
         <f t="shared" si="1"/>
         <v>799999</v>
       </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K17">
+      <c r="E17">
         <v>2</v>
       </c>
-      <c r="L17" s="8">
+      <c r="F17" s="8">
         <f t="shared" si="3"/>
         <v>4.0000800016000322E-5</v>
       </c>
-      <c r="M17">
+      <c r="G17">
         <f t="shared" si="5"/>
         <v>306</v>
       </c>
     </row>
-    <row r="18" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G18" t="str">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>800000 - 849999</v>
       </c>
-      <c r="H18" s="3">
+      <c r="B18" s="3">
         <f t="shared" si="4"/>
         <v>800000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="C18" s="3">
         <f t="shared" si="1"/>
         <v>849999</v>
       </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K18">
+      <c r="E18">
         <v>0</v>
       </c>
-      <c r="L18" s="8">
+      <c r="F18" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M18">
+      <c r="G18">
         <f t="shared" si="5"/>
         <v>306</v>
       </c>
     </row>
-    <row r="19" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G19" t="str">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>850000 - 899999</v>
       </c>
-      <c r="H19" s="3">
+      <c r="B19" s="3">
         <f t="shared" si="4"/>
         <v>850000</v>
       </c>
-      <c r="I19" s="3">
+      <c r="C19" s="3">
         <f t="shared" si="1"/>
         <v>899999</v>
       </c>
-      <c r="J19" s="3">
+      <c r="D19" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K19">
+      <c r="E19">
         <v>0</v>
       </c>
-      <c r="L19" s="8">
+      <c r="F19" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M19">
+      <c r="G19">
         <f t="shared" si="5"/>
         <v>306</v>
       </c>
     </row>
-    <row r="20" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G20" t="str">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>900000 - 949999</v>
       </c>
-      <c r="H20" s="3">
+      <c r="B20" s="3">
         <f t="shared" si="4"/>
         <v>900000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="C20" s="3">
         <f t="shared" si="1"/>
         <v>949999</v>
       </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K20">
+      <c r="E20">
         <v>0</v>
       </c>
-      <c r="L20" s="8">
+      <c r="F20" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M20">
+      <c r="G20">
         <f t="shared" si="5"/>
         <v>306</v>
       </c>
     </row>
-    <row r="21" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G21" t="str">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>950000 - 999999</v>
       </c>
-      <c r="H21" s="3">
+      <c r="B21" s="3">
         <f t="shared" si="4"/>
         <v>950000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="C21" s="3">
         <f t="shared" si="1"/>
         <v>999999</v>
       </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K21">
+      <c r="E21">
         <v>1</v>
       </c>
-      <c r="L21" s="8">
+      <c r="F21" s="8">
         <f t="shared" si="3"/>
         <v>2.0000400008000161E-5</v>
       </c>
-      <c r="M21">
+      <c r="G21">
         <f t="shared" si="5"/>
         <v>307</v>
       </c>
     </row>
-    <row r="22" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G22" t="str">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>1000000 - 1049999</v>
       </c>
-      <c r="H22" s="3">
+      <c r="B22" s="3">
         <f t="shared" si="4"/>
         <v>1000000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="C22" s="3">
         <f t="shared" si="1"/>
         <v>1049999</v>
       </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K22">
+      <c r="E22">
         <v>0</v>
       </c>
-      <c r="L22" s="8">
+      <c r="F22" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M22">
+      <c r="G22">
         <f t="shared" si="5"/>
         <v>307</v>
       </c>
     </row>
-    <row r="23" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G23" t="str">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>1050000 - 1099999</v>
       </c>
-      <c r="H23" s="3">
+      <c r="B23" s="3">
         <f t="shared" si="4"/>
         <v>1050000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="C23" s="3">
         <f t="shared" si="1"/>
         <v>1099999</v>
       </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K23">
+      <c r="E23">
         <v>0</v>
       </c>
-      <c r="L23" s="8">
+      <c r="F23" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M23">
+      <c r="G23">
         <f t="shared" si="5"/>
         <v>307</v>
       </c>
     </row>
-    <row r="24" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G24" t="str">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="str">
         <f t="shared" si="0"/>
         <v>1100000 - 1149999</v>
       </c>
-      <c r="H24" s="3">
+      <c r="B24" s="3">
         <f t="shared" si="4"/>
         <v>1100000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="C24" s="3">
         <f t="shared" si="1"/>
         <v>1149999</v>
       </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K24">
+      <c r="E24">
         <v>1</v>
       </c>
-      <c r="L24" s="8">
+      <c r="F24" s="8">
         <f t="shared" si="3"/>
         <v>2.0000400008000161E-5</v>
       </c>
-      <c r="M24">
+      <c r="G24">
         <f t="shared" si="5"/>
         <v>308</v>
       </c>
     </row>
-    <row r="25" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G25" t="str">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" t="str">
         <f t="shared" si="0"/>
         <v>1150000 - 1199999</v>
       </c>
-      <c r="H25" s="3">
+      <c r="B25" s="3">
         <f t="shared" si="4"/>
         <v>1150000</v>
       </c>
-      <c r="I25" s="3">
+      <c r="C25" s="3">
         <f t="shared" si="1"/>
         <v>1199999</v>
       </c>
-      <c r="J25" s="3">
+      <c r="D25" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K25">
+      <c r="E25">
         <v>0</v>
       </c>
-      <c r="L25" s="8">
+      <c r="F25" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M25">
+      <c r="G25">
         <f t="shared" si="5"/>
         <v>308</v>
       </c>
     </row>
-    <row r="26" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G26" t="str">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="str">
         <f t="shared" si="0"/>
         <v>1200000 - 1249999</v>
       </c>
-      <c r="H26" s="3">
+      <c r="B26" s="3">
         <f t="shared" si="4"/>
         <v>1200000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="C26" s="3">
         <f t="shared" si="1"/>
         <v>1249999</v>
       </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K26">
+      <c r="E26">
         <v>0</v>
       </c>
-      <c r="L26" s="8">
+      <c r="F26" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M26">
+      <c r="G26">
         <f t="shared" si="5"/>
         <v>308</v>
       </c>
     </row>
-    <row r="27" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G27" t="str">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="str">
         <f t="shared" si="0"/>
         <v>1250000 - 1299999</v>
       </c>
-      <c r="H27" s="3">
+      <c r="B27" s="3">
         <f t="shared" si="4"/>
         <v>1250000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="C27" s="3">
         <f t="shared" si="1"/>
         <v>1299999</v>
       </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K27">
+      <c r="E27">
         <v>0</v>
       </c>
-      <c r="L27" s="8">
+      <c r="F27" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M27">
+      <c r="G27">
         <f t="shared" si="5"/>
         <v>308</v>
       </c>
     </row>
-    <row r="28" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G28" t="str">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="str">
         <f t="shared" si="0"/>
         <v>1300000 - 1349999</v>
       </c>
-      <c r="H28" s="3">
+      <c r="B28" s="3">
         <f t="shared" si="4"/>
         <v>1300000</v>
       </c>
-      <c r="I28" s="3">
+      <c r="C28" s="3">
         <f t="shared" si="1"/>
         <v>1349999</v>
       </c>
-      <c r="J28" s="3">
+      <c r="D28" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K28">
+      <c r="E28">
         <v>0</v>
       </c>
-      <c r="L28" s="8">
+      <c r="F28" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M28">
+      <c r="G28">
         <f t="shared" si="5"/>
         <v>308</v>
       </c>
     </row>
-    <row r="29" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G29" t="str">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="str">
         <f t="shared" si="0"/>
         <v>1350000 - 1399999</v>
       </c>
-      <c r="H29" s="3">
+      <c r="B29" s="3">
         <f t="shared" si="4"/>
         <v>1350000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="C29" s="3">
         <f t="shared" si="1"/>
         <v>1399999</v>
       </c>
-      <c r="J29" s="3">
+      <c r="D29" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K29">
+      <c r="E29">
         <v>1</v>
       </c>
-      <c r="L29" s="8">
+      <c r="F29" s="8">
         <f t="shared" si="3"/>
         <v>2.0000400008000161E-5</v>
       </c>
-      <c r="M29">
+      <c r="G29">
         <f t="shared" si="5"/>
         <v>309</v>
       </c>
     </row>
-    <row r="30" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G30" t="str">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="str">
         <f t="shared" si="0"/>
         <v>1400000 - 1449999</v>
       </c>
-      <c r="H30" s="3">
+      <c r="B30" s="3">
         <f t="shared" si="4"/>
         <v>1400000</v>
       </c>
-      <c r="I30" s="3">
+      <c r="C30" s="3">
         <f t="shared" si="1"/>
         <v>1449999</v>
       </c>
-      <c r="J30" s="3">
+      <c r="D30" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K30">
+      <c r="E30">
         <v>0</v>
       </c>
-      <c r="L30" s="8">
+      <c r="F30" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M30">
+      <c r="G30">
         <f t="shared" si="5"/>
         <v>309</v>
       </c>
     </row>
-    <row r="31" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G31" t="str">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="str">
         <f t="shared" si="0"/>
         <v>1450000 - 1499999</v>
       </c>
-      <c r="H31" s="3">
+      <c r="B31" s="3">
         <f t="shared" si="4"/>
         <v>1450000</v>
       </c>
-      <c r="I31" s="3">
+      <c r="C31" s="3">
         <f t="shared" si="1"/>
         <v>1499999</v>
       </c>
-      <c r="J31" s="3">
+      <c r="D31" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K31">
+      <c r="E31">
         <v>0</v>
       </c>
-      <c r="L31" s="8">
+      <c r="F31" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M31">
+      <c r="G31">
         <f t="shared" si="5"/>
         <v>309</v>
       </c>
     </row>
-    <row r="32" spans="7:13" x14ac:dyDescent="0.2">
-      <c r="G32" t="str">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="str">
         <f t="shared" si="0"/>
         <v>1500000 - 1549999</v>
       </c>
-      <c r="H32" s="3">
+      <c r="B32" s="3">
         <f t="shared" si="4"/>
         <v>1500000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="C32" s="3">
         <f t="shared" si="1"/>
         <v>1549999</v>
       </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K32">
+      <c r="E32">
         <v>0</v>
       </c>
-      <c r="L32" s="8">
+      <c r="F32" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M32">
+      <c r="G32">
         <f t="shared" si="5"/>
         <v>309</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="G33" t="str">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" t="str">
         <f t="shared" si="0"/>
         <v>1550000 - 1599999</v>
       </c>
-      <c r="H33" s="3">
+      <c r="B33" s="3">
         <f t="shared" si="4"/>
         <v>1550000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="C33" s="3">
         <f t="shared" si="1"/>
         <v>1599999</v>
       </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K33">
+      <c r="E33">
         <v>1</v>
       </c>
-      <c r="L33" s="8">
+      <c r="F33" s="8">
         <f t="shared" si="3"/>
         <v>2.0000400008000161E-5</v>
       </c>
-      <c r="M33">
+      <c r="G33">
         <f t="shared" si="5"/>
         <v>310</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="G34" t="str">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
         <f t="shared" si="0"/>
         <v>1600000 - 1649999</v>
       </c>
-      <c r="H34" s="3">
+      <c r="B34" s="3">
         <f t="shared" si="4"/>
         <v>1600000</v>
       </c>
-      <c r="I34" s="3">
+      <c r="C34" s="3">
         <f t="shared" si="1"/>
         <v>1649999</v>
       </c>
-      <c r="J34" s="3">
+      <c r="D34" s="3">
         <f t="shared" si="2"/>
         <v>49999</v>
       </c>
-      <c r="K34">
+      <c r="E34">
         <v>0</v>
       </c>
-      <c r="L34" s="8">
+      <c r="F34" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M34">
+      <c r="G34">
         <f t="shared" si="5"/>
         <v>310</v>
       </c>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35">
         <v>0</v>
       </c>
-      <c r="L35" s="3"/>
-      <c r="M35">
+      <c r="F35" s="3"/>
+      <c r="G35">
         <f t="shared" si="5"/>
         <v>310</v>
       </c>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="21" type="noConversion"/>
@@ -25920,15 +26026,15 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>35</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -25946,7 +26052,7 @@
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -26342,7 +26448,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="11">
         <v>0.22903225806451613</v>
